--- a/assets/forms/F17_연간추진일정표_작성예시_5학년SW.xlsx
+++ b/assets/forms/F17_연간추진일정표_작성예시_5학년SW.xlsx
@@ -1827,7 +1827,7 @@
     <row r="10">
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>【2026. 12.∼2027. 1.】</t>
+          <t>【2027. 1. ○.】</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>학교교육과정·학년교육과정에 활동 반영, 교수·학습자료(과정안·활동지) 준비</t>
+          <t>학교교육과정위원회 협의, 학교교육과정·학년교육과정에 활동 반영, 교수·학습자료(과정안·활동지) 준비</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
